--- a/.cursor/scratch/tax_turbo_parts/MERCURY 8291.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/MERCURY 8291.xlsx
@@ -505,7 +505,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. Do not treat BoA 9922 draws or Koziol/Ariadne $150k as P&amp;L until confirmed. Not tax advice.</t>
+          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
           <t>DAVID AARON LIMITED</t>
         </is>
       </c>
-      <c r="C24" s="10" t="n">
+      <c r="C24" s="8" t="n">
         <v>13595</v>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1791,19 +1791,19 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>ART_SALE</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>ADVISORY</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>David Aaron Limited — proposed art sale</t>
+          <t>David Aaron Limited — consultant fee</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>London antiquities dealer; Request or Invoice Payment $13,595. Booked as a proposed sale (yellow) — confirm object / whether this is a purchase refund.</t>
+          <t>User 2026-09-20: consultant fee, not a sale. Hits EPGC Consultant June $13,595. Not Art Sales.</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
           <t>JACK EDWARD KOZIOL &amp; TRACY HOFFMAN</t>
         </is>
       </c>
-      <c r="C50" s="10" t="n">
+      <c r="C50" s="4" t="n">
         <v>150000</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
@@ -3356,9 +3356,9 @@
           <t>PASS_THROUGH</t>
         </is>
       </c>
-      <c r="F50" s="13" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>Incoming wire /BNF/Per your request. Next-day $150,000 OUT to Ariadne Demirjian LLC. Proposed pass-through — not income unless you say it is a sale.</t>
+          <t>User 2026-09-20: pass-through, not a sale. Incoming wire /BNF/Per your request. Next-day $150,000 OUT to Ariadne Demirjian LLC. Not P&amp;L.</t>
         </is>
       </c>
     </row>
@@ -3403,7 +3403,7 @@
           <t>Ariadne Demirjian LLC</t>
         </is>
       </c>
-      <c r="C51" s="10" t="n">
+      <c r="C51" s="4" t="n">
         <v>-150000</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
@@ -3416,9 +3416,9 @@
           <t>PASS_THROUGH</t>
         </is>
       </c>
-      <c r="F51" s="13" t="inlineStr">
-        <is>
-          <t>HOLD</t>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>Same window as Koziol $150,000 IN. Proposed pass-through — not COGS/expense unless you say it is a purchase.</t>
+          <t>User 2026-09-20: pass-through, not a purchase. Same window as Koziol $150,000 IN. Not P&amp;L.</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/MERCURY 8291.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/MERCURY 8291.xlsx
@@ -505,7 +505,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Not tax advice.</t>
+          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
           <t>Wise Inc</t>
         </is>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C27" s="8" t="n">
         <v>-334.17</v>
       </c>
       <c r="D27" s="3" t="inlineStr">
@@ -1971,19 +1971,19 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>ASK</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>ASK</t>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>EPGC_EXPENSE</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>Wise — vendor / COGS / other</t>
+          <t>Wise — expertise write-ups (Consultant Fees)</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>International payment from EPGC. Not reimbursed. COGS, advisory cost, or personal?</t>
+          <t>User 2026-09-20: business expense (expertise write-ups). Hits EPGC Consultant Fees July $334.17. Not COGS, not reimbursed. Distinct from Dec Wise $565.75 (EOEB reimburse).</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
           <t>Wise Inc</t>
         </is>
       </c>
-      <c r="C54" s="10" t="n">
+      <c r="C54" s="8" t="n">
         <v>-658.63</v>
       </c>
       <c r="D54" s="3" t="inlineStr">
@@ -3591,19 +3591,19 @@
           <t>OUT</t>
         </is>
       </c>
-      <c r="E54" s="11" t="inlineStr">
-        <is>
-          <t>ASK</t>
-        </is>
-      </c>
-      <c r="F54" s="11" t="inlineStr">
-        <is>
-          <t>ASK</t>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>EPGC_EXPENSE</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>Wise — vendor / COGS / other</t>
+          <t>Wise — expertise write-ups (Consultant Fees)</t>
         </is>
       </c>
       <c r="H54" s="3" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>International payment from EPGC. Not reimbursed. COGS, advisory cost, or personal?</t>
+          <t>User 2026-09-20: business expense (expertise write-ups). Hits EPGC Consultant Fees October $658.63. Not COGS, not reimbursed. Distinct from Dec Wise $565.75 (EOEB reimburse).</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/MERCURY 8291.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/MERCURY 8291.xlsx
@@ -505,7 +505,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Not tax advice.</t>
+          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Aquinas Hobor $1,000 (2/4) is LOCKED books sold (EPGC Art Sales February; Cost TBD). Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
           <t>AQUINAS HOBOR</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n">
+      <c r="C8" s="8" t="n">
         <v>1000</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -831,24 +831,24 @@
           <t>IN</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>ASK</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>ASK</t>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>ART_SALE</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Aquinas Hobor $1,000</t>
+          <t>Books sold to Aquinas Hobor — Sale Price</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>Prior-year buyer (Saharan bracelets 2022). 2025 sale, leftover, or something else?</t>
+          <t>User 2026-09-20: books sold to Aquinas. Hits EPGC Art Sales February $1,000. Cost / titles TBD (not in I8 net until Cost). Distinct from 2022 Saharan bracelets sale.</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/MERCURY 8291.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/MERCURY 8291.xlsx
@@ -723,7 +723,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>EOEB $1,000 — Canosan horse vs advisory</t>
+          <t>EOEB $1,000 — Canosan horse vs advisory (STILL OPEN)</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
-          <t>Art Sales has Canosan Terracotta Horse to Erdal $1,000. This cash is EOEB, not Erdal. Sale or advisory invoice?</t>
+          <t>STILL OPEN after mixed-pattern confirm. Art Sales has Canosan Terracotta Horse to Erdal $1,000. This cash is EOEB, not Erdal. Sale of the horse, advisory invoice, or other? Not allocated.</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Books sold to Aquinas Hobor — Sale Price</t>
+          <t>Books (titles TBD) — Sale Price</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
-          <t>User 2026-09-20: books sold to Aquinas. Hits EPGC Art Sales February $1,000. Cost / titles TBD (not in I8 net until Cost). Distinct from 2022 Saharan bracelets sale.</t>
+          <t>User 2026-09-20: book SALE to Aquinas Hobor. Hits EPGC Art Sales February +$1,000. Art Sales register: Books (titles TBD), Cost TBD. Not in Income I8 until Cost is known (same as Sale 6428).</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>Invoice / MAKE A PAYMENT. Not matched to an Art Sales object. Proposed advisory (Consultant) until you say otherwise.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>Invoice / MAKE A PAYMENT. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>Invoice / MAKE A PAYMENT. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>Invoice / MAKE A PAYMENT. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>Invoice / MAKE A PAYMENT. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>Auto-Routing Request or Invoice Payment. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>L5 — sale vs art advisory</t>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>Auto-Routing Request or Invoice Payment. Same invoice pattern as EOEB. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>L5 — sale vs art advisory</t>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>Auto-Routing Request or Invoice Payment. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>L5 $50,000 — sale vs art advisory vs pass-through</t>
+          <t>L5 $50,000 — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>Largest L5 invoice. Sale of an object, advisory, or pass-through? Same week as Aysel $50k IN and Fortuna $45k OUT.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK. Same week as Aysel $50k IN and Fortuna $45k OUT.</t>
         </is>
       </c>
     </row>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>L5 — sale vs art advisory</t>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>L5 — sale vs art advisory</t>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H49" s="3" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -3483,7 +3483,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>L5 — sale vs art advisory</t>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H52" s="3" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>EOEB — sale vs art advisory</t>
+          <t>EOEB — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: EOEB LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump EOEB remainder $130,270 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>L5 — sale vs art advisory</t>
+          <t>L5 — mixed unallocated (sale vs advisory)</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>Auto-Routing. Proposed advisory until confirmed.</t>
+          <t>User 2026-09-20: L5 LLC mixed art sales AND advisory/consultant fees. Pattern confirmed; this invoice still unallocated. Do NOT dump L5 remainder $87,396.32 onto Consultant or Art Sales. Invoice-level split still ASK.</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/MERCURY 8291.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/MERCURY 8291.xlsx
@@ -505,7 +505,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Aquinas Hobor $1,000 (2/4) is LOCKED books sold (EPGC Art Sales February; Cost TBD). Not tax advice.</t>
+          <t>Mercury Checking 8291 — EPGC LLC (Choice Financial) 2025. 64 unique cash transactions (Monarch IDs). Native Mercury CSV 2026-09-20 is the same 8291 year — 0 new unique Sent cash. Coinbase ACH = investment. Newstar = jewelry COGS on intaglios/gems/scarabs. Fortuna Venus $20k (5/9) + Roman Gold Belt $45k (7/21) LOCKED inventory (not sold Cost). BoA 9922 draws and Koziol/Ariadne $150k are LOCKED not-P&amp;L (pass-through / owner transfer). David Aaron $13,595 is LOCKED EPGC Consultant (June). Wise $334.17 + $658.63 are LOCKED EPGC Consultant Fees (expertise write-ups). Aquinas Hobor $1,000 (2/4) is LOCKED books sold (EPGC Art Sales February; Cost TBD). Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -623,12 +623,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Merchant name: Erdal Dere (Fortuna)</t>
+          <t>Merchant name: Erdal Dere (Fortuna); Mercury native: J.K. New York Collection | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
-          <t>Fortuna / Erdal Dere. Matches Art Sales Cost $13,000; Berk sold it 1/10 for $14,000.</t>
+          <t>Fortuna / Erdal Dere. Mercury native note: J.K. New York Collection. Matches Art Sales Cost $13,000; Berk sold it 1/10 for $14,000. Same-day Cancelled ACH to Erdal Dere (closed) is not cash.</t>
         </is>
       </c>
     </row>
@@ -983,7 +983,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Merchant name: Jamal M Rifai</t>
+          <t>Merchant name: Jamal M Rifai; Mercury native: via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Merchant name: Jamal M Rifai</t>
+          <t>Merchant name: Jamal M Rifai; Mercury native: From EPGC LLC via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Merchant name: Plutus &amp; Mnemosyne, LLC</t>
+          <t>Merchant name: Plutus &amp; Mnemosyne, LLC; Mercury native: via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Merchant name: Plutus &amp; Mnemosyne, LLC</t>
+          <t>Merchant name: Plutus &amp; Mnemosyne, LLC; Mercury native: From EPGC LLC via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -1543,7 +1543,7 @@
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C20" s="10" t="n">
+      <c r="C20" s="4" t="n">
         <v>-20000</v>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1556,14 +1556,14 @@
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>ASK</t>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>Fortuna / Erdal — inventory vs other</t>
+          <t>Bronze head of a goddess, likely Venus — inventory Cost</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Merchant name: Erdal Dere (Fortuna)</t>
+          <t>Merchant name: Erdal Dere (Fortuna); Mercury native: For bronze head of a goddess, likely Venus | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>After seals $13,000. Object name? Inventory purchase (COGS when sold) or something else?</t>
+          <t>Mercury native 2025 CSV note: 'For bronze head of a goddess, likely Venus'. Inventory purchase from Fortuna / Erdal. Not sold on 2025 Art Sales — parked Cost, not in sold-lot Cost (avoid double count). Not dumped onto Consultant or Art Sales P&amp;L.</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Aysel Dere $50,000 IN</t>
+          <t>Aysel Dere $50,000 IN on Monarch — NOT on Mercury native Sent</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>Same week as L5 $50k, Fortuna $45k OUT (7/21), Erdal $26k IN (7/24). Sale, family/related transfer, or inventory reverse?</t>
+          <t>Monarch 7/18 +$50,000 IN. Mercury native 2025 CSV (user upload 2026-09-20) has no Sent Aysel cash. Native has Failed $50,000 OUT 7/17 'Recipient account does not exist'. Keep on ASK — do not dump onto Art Sales or Consultant. Is the Monarch IN a phantom of the failed send?</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
           <t>Erdal Dere (Fortuna)</t>
         </is>
       </c>
-      <c r="C32" s="10" t="n">
+      <c r="C32" s="4" t="n">
         <v>-45000</v>
       </c>
       <c r="D32" s="3" t="inlineStr">
@@ -2276,14 +2276,14 @@
           <t>ART_PURCHASE</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>ASK</t>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>LOCKED</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Fortuna / Erdal — inventory vs other</t>
+          <t>Roman Gold Belt — inventory Cost</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>Merchant name: Erdal Dere (Fortuna)</t>
+          <t>Merchant name: Erdal Dere (Fortuna); Mercury native: From EPGC LLC via mercury.com | Roman Gold Belt | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>Object name? Ties to Aysel $50k / Erdal $26k the same week?</t>
+          <t>Mercury native 2025 CSV note: Roman Gold Belt. Inventory purchase from Fortuna / Erdal. Not sold on 2025 Art Sales — parked Cost, not in sold-lot Cost. Same week as L5 $50k / Monarch Aysel $50k ASK / Erdal $26k IN.</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>Fortuna / Erdal — inventory vs other</t>
+          <t>Fortuna / Erdal — object still unnamed</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>Merchant name: Erdal Dere (Fortuna)</t>
+          <t>Merchant name: Erdal Dere (Fortuna); Mercury native: From EPGC LLC via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>Object name?</t>
+          <t>Same $20,000 OUT as Mercury native initiated 2025-08-18 / Monarch posted 2025-08-15. No object name in the native memo ('From EPGC LLC via mercury.com'). Inventory vs other? Do not add to sold Cost until named. Not a second unique txn.</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>Merchant name: Newstar Jewelers</t>
+          <t>Merchant name: Newstar Jewelers; Mercury native: From EPGC LLC via mercury.com | 1 of 3 payments | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>Merchant name: Ariadne Demirjian LLC</t>
+          <t>Merchant name: Ariadne Demirjian LLC; Mercury native: via mercury.com; Vendor: Ariadne Demirjian LLC Roth 401k Account 5386-8600 | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>Merchant name: Newstar Jewelers</t>
+          <t>Merchant name: Newstar Jewelers; Mercury native: From EPGC LLC via mercury.com | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>From EPGC LLC via mercury.com 3 of 3; Merchant name: Newstar Jewelers</t>
+          <t>From EPGC LLC via mercury.com 3 of 3; Merchant name: Newstar Jewelers; Mercury native: From EPGC LLC via mercury.com 3 of 3 | Send Money transaction initiated on Mercury</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
